--- a/multiSchoolOutput/01_Royal_(Dick)_School_of_Veterinary_Studie/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_Royal_(Dick)_School_of_Veterinary_Studie/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
         <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -626,7 +626,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -668,12 +668,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -685,7 +685,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -727,12 +727,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -904,12 +904,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -980,7 +980,7 @@
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1098,7 +1098,7 @@
         <v>202</v>
       </c>
       <c r="F12" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1157,7 +1157,7 @@
         <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>202</v>
       </c>
       <c r="F14" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1334,7 +1334,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1452,7 +1452,7 @@
         <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1688,7 +1688,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2514,7 +2514,7 @@
         <v>202</v>
       </c>
       <c r="F36" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2632,7 +2632,7 @@
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2809,7 +2809,7 @@
         <v>202</v>
       </c>
       <c r="F41" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2868,7 +2868,7 @@
         <v>120</v>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2927,7 +2927,7 @@
         <v>202</v>
       </c>
       <c r="F43" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3045,7 +3045,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3104,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3222,7 +3222,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3281,7 +3281,7 @@
         <v>202</v>
       </c>
       <c r="F49" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3576,7 +3576,7 @@
         <v>125</v>
       </c>
       <c r="F54" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3694,7 +3694,7 @@
         <v>92</v>
       </c>
       <c r="F56" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3871,7 +3871,7 @@
         <v>120</v>
       </c>
       <c r="F59" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v>202</v>
       </c>
       <c r="F60" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4048,7 +4048,7 @@
         <v>120</v>
       </c>
       <c r="F62" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4225,7 +4225,7 @@
         <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4343,7 +4343,7 @@
         <v>202</v>
       </c>
       <c r="F67" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4461,7 +4461,7 @@
         <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4520,7 +4520,7 @@
         <v>120</v>
       </c>
       <c r="F70" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4638,7 +4638,7 @@
         <v>120</v>
       </c>
       <c r="F72" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4680,12 +4680,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0311_02_2.05</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4697,7 +4697,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4756,7 +4756,7 @@
         <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4874,7 +4874,7 @@
         <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4916,12 +4916,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4933,7 +4933,7 @@
         <v>4</v>
       </c>
       <c r="F77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4992,7 +4992,7 @@
         <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5051,7 +5051,7 @@
         <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5093,12 +5093,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5169,7 +5169,7 @@
         <v>202</v>
       </c>
       <c r="F81" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5211,12 +5211,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5228,7 +5228,7 @@
         <v>202</v>
       </c>
       <c r="F82" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5287,7 +5287,7 @@
         <v>120</v>
       </c>
       <c r="F83" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>202</v>
       </c>
       <c r="F84" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5388,12 +5388,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5523,7 +5523,7 @@
         <v>120</v>
       </c>
       <c r="F87" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5565,12 +5565,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5641,7 +5641,7 @@
         <v>92</v>
       </c>
       <c r="F89" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5759,7 +5759,7 @@
         <v>120</v>
       </c>
       <c r="F91" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5877,7 +5877,7 @@
         <v>120</v>
       </c>
       <c r="F93" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5995,7 +5995,7 @@
         <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -6037,12 +6037,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6096,12 +6096,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6113,7 +6113,7 @@
         <v>120</v>
       </c>
       <c r="F97" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6231,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6273,12 +6273,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6290,7 +6290,7 @@
         <v>120</v>
       </c>
       <c r="F100" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6349,7 +6349,7 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6467,7 +6467,7 @@
         <v>4</v>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6644,7 +6644,7 @@
         <v>125</v>
       </c>
       <c r="F106" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6703,7 +6703,7 @@
         <v>202</v>
       </c>
       <c r="F107" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6821,7 +6821,7 @@
         <v>125</v>
       </c>
       <c r="F109" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6880,7 +6880,7 @@
         <v>120</v>
       </c>
       <c r="F110" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6922,12 +6922,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6939,7 +6939,7 @@
         <v>125</v>
       </c>
       <c r="F111" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6998,7 +6998,7 @@
         <v>120</v>
       </c>
       <c r="F112" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7175,7 +7175,7 @@
         <v>120</v>
       </c>
       <c r="F115" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0008_00_G.251</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7293,7 +7293,7 @@
         <v>120</v>
       </c>
       <c r="F117" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -7335,12 +7335,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0005_02_2.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7411,7 +7411,7 @@
         <v>202</v>
       </c>
       <c r="F119" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0001_01_1.266</t>
+          <t>0112_-1_B.03</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7529,7 +7529,7 @@
         <v>202</v>
       </c>
       <c r="F121" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7588,7 +7588,7 @@
         <v>120</v>
       </c>
       <c r="F122" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7706,7 +7706,7 @@
         <v>120</v>
       </c>
       <c r="F124" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7824,7 +7824,7 @@
         <v>125</v>
       </c>
       <c r="F126" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0300_00_NG.02</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0311_02_2.05</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8058,7 +8058,7 @@
         <v>30</v>
       </c>
       <c r="F130" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8117,7 +8117,7 @@
         <v>120</v>
       </c>
       <c r="F131" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8294,7 +8294,7 @@
         <v>120</v>
       </c>
       <c r="F134" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8353,7 +8353,7 @@
         <v>120</v>
       </c>
       <c r="F135" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8572,12 +8572,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8589,7 +8589,7 @@
         <v>120</v>
       </c>
       <c r="F139" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -8631,12 +8631,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8648,7 +8648,7 @@
         <v>202</v>
       </c>
       <c r="F140" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8766,7 +8766,7 @@
         <v>202</v>
       </c>
       <c r="F142" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8825,7 +8825,7 @@
         <v>120</v>
       </c>
       <c r="F143" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8884,7 +8884,7 @@
         <v>202</v>
       </c>
       <c r="F144" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -8926,12 +8926,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0210_-1_B.51</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9002,7 +9002,7 @@
         <v>202</v>
       </c>
       <c r="F146" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9061,7 +9061,7 @@
         <v>125</v>
       </c>
       <c r="F147" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9120,7 +9120,7 @@
         <v>80</v>
       </c>
       <c r="F148" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9179,7 +9179,7 @@
         <v>120</v>
       </c>
       <c r="F149" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.B</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9592,7 +9592,7 @@
         <v>202</v>
       </c>
       <c r="F156" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0335_02_2.4</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10064,7 +10064,7 @@
         <v>15</v>
       </c>
       <c r="F164" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10241,7 +10241,7 @@
         <v>202</v>
       </c>
       <c r="F167" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10300,7 +10300,7 @@
         <v>125</v>
       </c>
       <c r="F168" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0115_00_G.22</t>
+          <t>0229_01_1.C</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10418,7 +10418,7 @@
         <v>202</v>
       </c>
       <c r="F170" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10536,7 +10536,7 @@
         <v>120</v>
       </c>
       <c r="F172" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -10578,12 +10578,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10595,7 +10595,7 @@
         <v>125</v>
       </c>
       <c r="F173" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -10637,12 +10637,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10654,7 +10654,7 @@
         <v>4</v>
       </c>
       <c r="F174" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10713,7 +10713,7 @@
         <v>120</v>
       </c>
       <c r="F175" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -10755,12 +10755,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0005_01_1.01</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10890,7 +10890,7 @@
         <v>92</v>
       </c>
       <c r="F178" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -10932,12 +10932,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10991,12 +10991,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0201_00_G.07</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -11107,12 +11107,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11166,12 +11166,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11242,7 +11242,7 @@
         <v>120</v>
       </c>
       <c r="F184" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -11284,12 +11284,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11301,7 +11301,7 @@
         <v>120</v>
       </c>
       <c r="F185" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11579,12 +11579,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_02_2.01</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11714,7 +11714,7 @@
         <v>120</v>
       </c>
       <c r="F192" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11950,7 +11950,7 @@
         <v>15</v>
       </c>
       <c r="F196" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12068,7 +12068,7 @@
         <v>4</v>
       </c>
       <c r="F198" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -12110,12 +12110,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12127,7 +12127,7 @@
         <v>4</v>
       </c>
       <c r="F199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12186,7 +12186,7 @@
         <v>4</v>
       </c>
       <c r="F200" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -12228,12 +12228,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12245,7 +12245,7 @@
         <v>4</v>
       </c>
       <c r="F201" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -12287,12 +12287,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12304,7 +12304,7 @@
         <v>4</v>
       </c>
       <c r="F202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -12346,12 +12346,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12363,7 +12363,7 @@
         <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -12405,12 +12405,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12422,7 +12422,7 @@
         <v>4</v>
       </c>
       <c r="F204" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -12464,12 +12464,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12481,7 +12481,7 @@
         <v>4</v>
       </c>
       <c r="F205" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -12523,12 +12523,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12540,7 +12540,7 @@
         <v>4</v>
       </c>
       <c r="F206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12599,7 +12599,7 @@
         <v>4</v>
       </c>
       <c r="F207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>

--- a/multiSchoolOutput/01_Royal_(Dick)_School_of_Veterinary_Studie/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/01_Royal_(Dick)_School_of_Veterinary_Studie/solution_weeks_9_10.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -626,7 +626,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -668,12 +668,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -685,7 +685,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -744,7 +744,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -845,12 +845,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -904,12 +904,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -980,7 +980,7 @@
         <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1039,7 +1039,7 @@
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1098,7 +1098,7 @@
         <v>202</v>
       </c>
       <c r="F12" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1216,7 +1216,7 @@
         <v>202</v>
       </c>
       <c r="F14" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1334,7 +1334,7 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1452,7 +1452,7 @@
         <v>125</v>
       </c>
       <c r="F18" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1688,7 +1688,7 @@
         <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1983,7 +1983,7 @@
         <v>30</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0335_05_5.2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2396,7 +2396,7 @@
         <v>30</v>
       </c>
       <c r="F34" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2514,7 +2514,7 @@
         <v>202</v>
       </c>
       <c r="F36" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2632,7 +2632,7 @@
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2809,7 +2809,7 @@
         <v>202</v>
       </c>
       <c r="F41" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2927,7 +2927,7 @@
         <v>202</v>
       </c>
       <c r="F43" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3045,7 +3045,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3087,12 +3087,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3104,7 +3104,7 @@
         <v>4</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3146,12 +3146,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_00_G.10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3163,7 +3163,7 @@
         <v>30</v>
       </c>
       <c r="F47" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3222,7 +3222,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3281,7 +3281,7 @@
         <v>202</v>
       </c>
       <c r="F49" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3576,7 +3576,7 @@
         <v>125</v>
       </c>
       <c r="F54" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3871,7 +3871,7 @@
         <v>120</v>
       </c>
       <c r="F59" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v>202</v>
       </c>
       <c r="F60" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4048,7 +4048,7 @@
         <v>120</v>
       </c>
       <c r="F62" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4166,7 +4166,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4225,7 +4225,7 @@
         <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4284,7 +4284,7 @@
         <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4343,7 +4343,7 @@
         <v>202</v>
       </c>
       <c r="F67" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4461,7 +4461,7 @@
         <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4520,7 +4520,7 @@
         <v>120</v>
       </c>
       <c r="F70" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0311_02_2.05</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4697,7 +4697,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4756,7 +4756,7 @@
         <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4857,12 +4857,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4874,7 +4874,7 @@
         <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4916,12 +4916,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4933,7 +4933,7 @@
         <v>4</v>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4992,7 +4992,7 @@
         <v>4</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5051,7 +5051,7 @@
         <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5093,12 +5093,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5169,7 +5169,7 @@
         <v>202</v>
       </c>
       <c r="F81" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5211,12 +5211,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5228,7 +5228,7 @@
         <v>202</v>
       </c>
       <c r="F82" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>202</v>
       </c>
       <c r="F84" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5388,12 +5388,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5405,7 +5405,7 @@
         <v>30</v>
       </c>
       <c r="F85" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5523,7 +5523,7 @@
         <v>120</v>
       </c>
       <c r="F87" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0228_-1_LG.09</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5877,7 +5877,7 @@
         <v>120</v>
       </c>
       <c r="F93" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5936,7 +5936,7 @@
         <v>30</v>
       </c>
       <c r="F94" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5995,7 +5995,7 @@
         <v>4</v>
       </c>
       <c r="F95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -6037,12 +6037,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6054,7 +6054,7 @@
         <v>30</v>
       </c>
       <c r="F96" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6231,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6273,12 +6273,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6290,7 +6290,7 @@
         <v>120</v>
       </c>
       <c r="F100" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6349,7 +6349,7 @@
         <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -6391,12 +6391,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6467,7 +6467,7 @@
         <v>4</v>
       </c>
       <c r="F103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6585,7 +6585,7 @@
         <v>30</v>
       </c>
       <c r="F105" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6627,12 +6627,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6644,7 +6644,7 @@
         <v>125</v>
       </c>
       <c r="F106" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6686,12 +6686,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6703,7 +6703,7 @@
         <v>202</v>
       </c>
       <c r="F107" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6821,7 +6821,7 @@
         <v>125</v>
       </c>
       <c r="F109" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7099,12 +7099,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7116,7 +7116,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0008_00_G.251</t>
+          <t>0001_01_1.266</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7411,7 +7411,7 @@
         <v>202</v>
       </c>
       <c r="F119" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7529,7 +7529,7 @@
         <v>202</v>
       </c>
       <c r="F121" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7588,7 +7588,7 @@
         <v>120</v>
       </c>
       <c r="F122" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7706,7 +7706,7 @@
         <v>120</v>
       </c>
       <c r="F124" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7765,7 +7765,7 @@
         <v>8</v>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0300_00_NG.02</t>
+          <t>0201_00_G.07</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0311_02_2.05</t>
+          <t>0335_01_1.9</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8058,7 +8058,7 @@
         <v>30</v>
       </c>
       <c r="F130" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8117,7 +8117,7 @@
         <v>120</v>
       </c>
       <c r="F131" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -8159,12 +8159,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8294,7 +8294,7 @@
         <v>120</v>
       </c>
       <c r="F134" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8353,7 +8353,7 @@
         <v>120</v>
       </c>
       <c r="F135" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Friday 10:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8572,12 +8572,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8589,7 +8589,7 @@
         <v>120</v>
       </c>
       <c r="F139" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -8631,12 +8631,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8648,7 +8648,7 @@
         <v>202</v>
       </c>
       <c r="F140" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8690,12 +8690,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8707,7 +8707,7 @@
         <v>120</v>
       </c>
       <c r="F141" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8766,7 +8766,7 @@
         <v>202</v>
       </c>
       <c r="F142" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8884,7 +8884,7 @@
         <v>202</v>
       </c>
       <c r="F144" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -8926,12 +8926,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9002,7 +9002,7 @@
         <v>202</v>
       </c>
       <c r="F146" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9061,7 +9061,7 @@
         <v>125</v>
       </c>
       <c r="F147" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9179,7 +9179,7 @@
         <v>120</v>
       </c>
       <c r="F149" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0229_01_1.B</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9592,7 +9592,7 @@
         <v>202</v>
       </c>
       <c r="F156" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 10:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0005_02_2.01</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9988,12 +9988,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0335_02_2.4</t>
+          <t>0300_00_NG.04</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10241,7 +10241,7 @@
         <v>202</v>
       </c>
       <c r="F167" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10300,7 +10300,7 @@
         <v>125</v>
       </c>
       <c r="F168" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -10342,12 +10342,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0229_01_1.C</t>
+          <t>0115_00_G.22</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10418,7 +10418,7 @@
         <v>202</v>
       </c>
       <c r="F170" t="n">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -10460,12 +10460,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10595,7 +10595,7 @@
         <v>125</v>
       </c>
       <c r="F173" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -10637,12 +10637,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10654,7 +10654,7 @@
         <v>4</v>
       </c>
       <c r="F174" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0005_02_2.01</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10932,12 +10932,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_04_4.2</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10949,7 +10949,7 @@
         <v>30</v>
       </c>
       <c r="F179" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -10991,12 +10991,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0201_00_G.07</t>
+          <t>0226_-1_LG.18</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="n">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0209_01_1.21</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11242,7 +11242,7 @@
         <v>120</v>
       </c>
       <c r="F184" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -11284,12 +11284,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0209_01_1.21</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Monday 13:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11301,7 +11301,7 @@
         <v>120</v>
       </c>
       <c r="F185" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tuesday 13:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wednesday 13:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0210_-1_B.51</t>
+          <t>0005_01_1.01</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0001_02_2.351</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 13:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12068,7 +12068,7 @@
         <v>4</v>
       </c>
       <c r="F198" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -12110,12 +12110,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12127,7 +12127,7 @@
         <v>4</v>
       </c>
       <c r="F199" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -12169,12 +12169,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12186,7 +12186,7 @@
         <v>4</v>
       </c>
       <c r="F200" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -12228,12 +12228,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12245,7 +12245,7 @@
         <v>4</v>
       </c>
       <c r="F201" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -12287,12 +12287,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12304,7 +12304,7 @@
         <v>4</v>
       </c>
       <c r="F202" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -12346,12 +12346,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12363,7 +12363,7 @@
         <v>4</v>
       </c>
       <c r="F203" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -12405,12 +12405,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12422,7 +12422,7 @@
         <v>4</v>
       </c>
       <c r="F204" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -12464,12 +12464,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12481,7 +12481,7 @@
         <v>4</v>
       </c>
       <c r="F205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -12523,12 +12523,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12540,7 +12540,7 @@
         <v>4</v>
       </c>
       <c r="F206" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12599,7 +12599,7 @@
         <v>4</v>
       </c>
       <c r="F207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
